--- a/output/2026-09-05_23_Slovenia_Podravska_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-05_23_Slovenia_Podravska_Depolverazione_Trattamento_aria.xlsx
@@ -575,7 +575,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Verificato via WebSearch (pagina ufficiale Kärcher, articolo siol.net sull'apertura del centro il 16 ottobre 2025). Centro Kärcher ufficiale/più grande in Slovenia, distinto da Techno Center Elesprom (indirizzo, telefono ed email differenti, confermato non essere un duplicato). Rivenditore/assistenza per apparecchiature professionali/industriali di pulizia e aspirazione. Telefono ed email confermati da fonte reale.</t>
+          <t>Verificato via WebSearch (pagina ufficiale Kärcher, articolo siol.net sull'apertura del centro il 16 ottobre 2025). Centro Kärcher ufficiale/più grande in Slovenia, distinto da Techno Center Elesprom (indirizzo, telefono ed email differenti, confermato non essere un duplicato). Rivenditore/assistenza per apparecchiature professionali/industriali di pulizia e aspirazione. Telefono ed email confermati da fonte reale. [DUPLICATO — vedi anche: 2026-09-05_20_Slovenia_Pomurska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
